--- a/reid_test/reid_test_template.xlsx
+++ b/reid_test/reid_test_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nutzer\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Githubs\IEEE-Technology-and-Society-Draft\reid_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC9C86C-9459-4FA5-80EB-7FAAD4C9EBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66006A7-2988-4A19-9D8E-CE27FC6043BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -455,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
@@ -1011,6 +1011,12 @@
       </c>
       <c r="G23" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <f>A11+A23</f>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
